--- a/LangMod/EN/Dialog/Drama/RQXDIalog.xlsx
+++ b/LangMod/EN/Dialog/Drama/RQXDIalog.xlsx
@@ -315,12 +315,12 @@
   </si>
   <si>
     <t xml:space="preserve">{おや}、わかっていない{な}。
-寛大にも{I}が{YOU}を見逃して、しかも金もやると言っているの{だが}。
+寛大にも{I}が{YOU}を見逃して、しかも駄賃もやると言っているの{だが}。
 人の好意を素直に受け取らない奴は痛い目にあってもらう{よ}！</t>
   </si>
   <si>
     <t xml:space="preserve">Oh, you don't seem to understand.
-I'm being generous enough to let you go and even give you money on top of that.
+I'm being generous enough to let you go and even give you tip on top of that.
 If you can't accept someone's kindness, then I'll have to teach you a painful lesson!</t>
   </si>
   <si>
@@ -924,37 +924,37 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="18a303"/>
+        <a:srgbClr val="18A303"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="0369a3"/>
+        <a:srgbClr val="0369A3"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="a33e03"/>
+        <a:srgbClr val="A33E03"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8e03a3"/>
+        <a:srgbClr val="8E03A3"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="c99c00"/>
+        <a:srgbClr val="C99C00"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="c9211e"/>
+        <a:srgbClr val="C9211E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ee"/>
+        <a:srgbClr val="0000EE"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="551a8b"/>
+        <a:srgbClr val="551A8B"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
